--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129805484</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129805482</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129805483</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129805484</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129805482</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129805483</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129805484</v>
+        <v>129805482</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421780</v>
+        <v>421820</v>
       </c>
       <c r="R2" t="n">
-        <v>6961939</v>
+        <v>6962017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129805482</v>
+        <v>129805483</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421820</v>
+        <v>421818</v>
       </c>
       <c r="R3" t="n">
-        <v>6962017</v>
+        <v>6961973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129805483</v>
+        <v>129805484</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421818</v>
+        <v>421780</v>
       </c>
       <c r="R4" t="n">
-        <v>6961973</v>
+        <v>6961939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805484</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>